--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_23-06-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_23-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Ecotherm_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86FE6B3-E71A-4510-B84F-DEAB06A0755A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C224E3-6D59-482E-A655-830A10FE84BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32430" yWindow="1665" windowWidth="21600" windowHeight="11550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="1290" windowWidth="21600" windowHeight="11550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="191">
   <si>
     <t>SKU</t>
   </si>
@@ -554,6 +554,45 @@
   </si>
   <si>
     <t>£95.89</t>
+  </si>
+  <si>
+    <t>£17.00</t>
+  </si>
+  <si>
+    <t>£24.00</t>
+  </si>
+  <si>
+    <t>£27.50</t>
+  </si>
+  <si>
+    <t>£32.50</t>
+  </si>
+  <si>
+    <t>£35.50</t>
+  </si>
+  <si>
+    <t>£36.25</t>
+  </si>
+  <si>
+    <t>£40.00</t>
+  </si>
+  <si>
+    <t>£43.00</t>
+  </si>
+  <si>
+    <t>£44.75</t>
+  </si>
+  <si>
+    <t>£53.75</t>
+  </si>
+  <si>
+    <t>£60.50</t>
+  </si>
+  <si>
+    <t>£65.50</t>
+  </si>
+  <si>
+    <t>£66.50</t>
   </si>
 </sst>
 </file>
@@ -995,7 +1034,7 @@
         <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
@@ -1045,7 +1084,7 @@
         <v>33</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J3" t="s">
         <v>22</v>
@@ -1095,7 +1134,7 @@
         <v>43</v>
       </c>
       <c r="I4" t="s">
-        <v>40</v>
+        <v>179</v>
       </c>
       <c r="J4" t="s">
         <v>22</v>
@@ -1145,7 +1184,7 @@
         <v>53</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
@@ -1195,7 +1234,7 @@
         <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>181</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
@@ -1245,7 +1284,7 @@
         <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>182</v>
       </c>
       <c r="J7" t="s">
         <v>22</v>
@@ -1295,7 +1334,7 @@
         <v>83</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>183</v>
       </c>
       <c r="J8" t="s">
         <v>22</v>
@@ -1345,7 +1384,7 @@
         <v>93</v>
       </c>
       <c r="I9" t="s">
-        <v>90</v>
+        <v>184</v>
       </c>
       <c r="J9" t="s">
         <v>22</v>
@@ -1395,7 +1434,7 @@
         <v>103</v>
       </c>
       <c r="I10" t="s">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="J10" t="s">
         <v>22</v>
@@ -1445,7 +1484,7 @@
         <v>113</v>
       </c>
       <c r="I11" t="s">
-        <v>110</v>
+        <v>186</v>
       </c>
       <c r="J11" t="s">
         <v>22</v>
@@ -1495,7 +1534,7 @@
         <v>121</v>
       </c>
       <c r="I12" t="s">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="J12" t="s">
         <v>22</v>
@@ -1545,7 +1584,7 @@
         <v>130</v>
       </c>
       <c r="I13" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="J13" t="s">
         <v>22</v>
@@ -1595,7 +1634,7 @@
         <v>139</v>
       </c>
       <c r="I14" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="J14" t="s">
         <v>22</v>
@@ -1645,7 +1684,7 @@
         <v>149</v>
       </c>
       <c r="I15" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="J15" t="s">
         <v>22</v>
@@ -1695,7 +1734,7 @@
         <v>159</v>
       </c>
       <c r="I16" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="J16" t="s">
         <v>22</v>
